--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -5431,7 +5431,7 @@
         <v>132617558</v>
       </c>
       <c r="B42" t="n">
-        <v>80351</v>
+        <v>80513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 13423-2026 artfynd.xlsx
+++ b/artfynd/A 13423-2026 artfynd.xlsx
@@ -5431,7 +5431,7 @@
         <v>132617558</v>
       </c>
       <c r="B42" t="n">
-        <v>80513</v>
+        <v>80517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
